--- a/datatables/datas/__tables__.xlsx
+++ b/datatables/datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -126,6 +126,33 @@
   </si>
   <si>
     <t>节点定义表.xlsx</t>
+  </si>
+  <si>
+    <t>TbGameCampaign</t>
+  </si>
+  <si>
+    <t>GameCampaign</t>
+  </si>
+  <si>
+    <t>游戏副本定义表.xlsx</t>
+  </si>
+  <si>
+    <t>TbGameButton</t>
+  </si>
+  <si>
+    <t>GameButton</t>
+  </si>
+  <si>
+    <t>游戏按钮定义表.xlsx</t>
+  </si>
+  <si>
+    <t>TbAutoGameButton</t>
+  </si>
+  <si>
+    <t>AutoGameButton</t>
+  </si>
+  <si>
+    <t>自动游戏按钮定义表.xlsx</t>
   </si>
 </sst>
 </file>
@@ -741,14 +768,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1070,8 +1094,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="29.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
@@ -1204,20 +1228,46 @@
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:11">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" customFormat="1" spans="1:11">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:11">
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
